--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -390,7 +390,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -570,7 +570,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -599,7 +599,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -679,7 +679,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -969,7 +969,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1127,7 +1127,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1150,7 +1150,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1249,7 +1249,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1514,7 +1514,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1546,7 +1546,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1605,7 +1605,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1638,7 +1638,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1650,7 +1650,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1678,7 +1678,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1758,7 +1758,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1808,7 +1808,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1841,7 +1841,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1878,7 +1878,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -1900,7 +1900,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2370,7 +2370,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.5859375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.9921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -4192,7 +4192,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>192</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>215</v>
       </c>
@@ -4794,7 +4794,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>230</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>244</v>
       </c>
@@ -5396,7 +5396,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>262</v>
       </c>
@@ -5880,7 +5880,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>298</v>
       </c>
@@ -8414,7 +8414,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>347</v>
       </c>
@@ -8778,7 +8778,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>374</v>
       </c>
@@ -9502,7 +9502,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>423</v>
       </c>
@@ -9864,7 +9864,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>429</v>
       </c>
@@ -10108,7 +10108,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>450</v>
       </c>
@@ -10228,7 +10228,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>458</v>
       </c>
@@ -10348,7 +10348,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>467</v>
       </c>
@@ -10470,7 +10470,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>475</v>
       </c>
@@ -12758,7 +12758,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>608</v>
       </c>
@@ -13240,7 +13240,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
         <v>618</v>
       </c>
@@ -13362,7 +13362,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
         <v>624</v>
       </c>
@@ -13484,7 +13484,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
         <v>633</v>
       </c>
@@ -13852,12 +13852,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP95">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>0.9.5</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.5</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.61</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.61</t>
+    <t>0.9.71</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.71</t>
+    <t>0.9.72</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.72</t>
+    <t>0.9.73</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.73</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.74</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
+++ b/VitalSigns/TestBuild/StructureDefinition-no-domain-VitalSigns-Observation-oxygensaturation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.74</t>
   </si>
   <si>
     <t>Name</t>
